--- a/TestData/TBS.xlsx
+++ b/TestData/TBS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\TBS_Playwright\TBS_1099W2\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\TBS_Playwright\TBS_1099W2\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F656E466-BB40-4EA6-A07D-F8D893799860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADD0E93-131B-4598-8DC0-FCD9C5FF121D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFILE" sheetId="1" r:id="rId1"/>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId33" roundtripDataChecksum="KWJLnYoYn+54jAvnUIl6lkp/DomDMjJnzxl+jlio9NE="/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="257">
   <si>
     <t>Scenario_ID</t>
   </si>
@@ -126,63 +123,9 @@
     <t>Payer Country</t>
   </si>
   <si>
-    <t>Recipient</t>
-  </si>
-  <si>
-    <t>Recipient Country</t>
-  </si>
-  <si>
-    <t>Account_Number</t>
-  </si>
-  <si>
-    <t>13_FATCA_Filing_Requirement</t>
-  </si>
-  <si>
-    <t>2nd_TIN_Not</t>
-  </si>
-  <si>
-    <t>Nonemployee_Compensation</t>
-  </si>
-  <si>
-    <t>Payer_Made_Direct_Sales_Totalling_$5,000</t>
-  </si>
-  <si>
     <t>Federal_Income_Tax_Withheld</t>
   </si>
   <si>
-    <t>State_Tax_Withheld</t>
-  </si>
-  <si>
-    <t>State_Info</t>
-  </si>
-  <si>
-    <t>Payer's_State_No</t>
-  </si>
-  <si>
-    <t>State_Income</t>
-  </si>
-  <si>
-    <t>State Recon</t>
-  </si>
-  <si>
-    <t>Form A-3 Deposit Schedule</t>
-  </si>
-  <si>
-    <t>Tax Remitted</t>
-  </si>
-  <si>
-    <t>First_Quarter_Tax_Due</t>
-  </si>
-  <si>
-    <t>Second_Quarter_Tax_Due</t>
-  </si>
-  <si>
-    <t>Third_Quarter_Tax_Due</t>
-  </si>
-  <si>
-    <t>Fourth_Quarter_Tax_Due</t>
-  </si>
-  <si>
     <t>Federal Filling</t>
   </si>
   <si>
@@ -213,12 +156,6 @@
     <t>USA</t>
   </si>
   <si>
-    <t>Valid</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Alaska (AK)</t>
   </si>
   <si>
@@ -456,21 +393,6 @@
     <t>Delaware (DE)</t>
   </si>
   <si>
-    <t>State Count</t>
-  </si>
-  <si>
-    <t>State_Info_2</t>
-  </si>
-  <si>
-    <t>Payer's_State_No_2</t>
-  </si>
-  <si>
-    <t>State_Income_2</t>
-  </si>
-  <si>
-    <t>State_Tax_Withheld_2</t>
-  </si>
-  <si>
     <t>Hawaii (HI)</t>
   </si>
   <si>
@@ -510,9 +432,6 @@
     <t>RANDOM</t>
   </si>
   <si>
-    <t>Recipient State</t>
-  </si>
-  <si>
     <t>Winner State</t>
   </si>
   <si>
@@ -831,9 +750,6 @@
     <t>DELETE</t>
   </si>
   <si>
-    <t>DELETE-FORM</t>
-  </si>
-  <si>
     <t>Form NEC - Federal - Delete Return</t>
   </si>
   <si>
@@ -867,27 +783,49 @@
     <t>Form NEC - Bulk Upload - Recipient only</t>
   </si>
   <si>
-    <t>BanditCash</t>
-  </si>
-  <si>
-    <t>Credits</t>
-  </si>
-  <si>
-    <t>Discount</t>
-  </si>
-  <si>
-    <t>SaveForLaterAndContinue</t>
+    <t>EIN</t>
+  </si>
+  <si>
+    <t>Employee TIN</t>
+  </si>
+  <si>
+    <t>Employee Country</t>
+  </si>
+  <si>
+    <t>Employee State</t>
+  </si>
+  <si>
+    <t>Payer TIN</t>
+  </si>
+  <si>
+    <t>SSN</t>
+  </si>
+  <si>
+    <t>FinalPDF</t>
+  </si>
+  <si>
+    <t>CardDetails</t>
+  </si>
+  <si>
+    <t>PostalMailing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -977,6 +915,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1022,7 +980,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1060,49 +1018,80 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1111,120 +1100,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
+    <cellStyle name="Hyperlink 2" xfId="5" xr:uid="{D2B34FF0-27B0-4AD5-91B6-1C6AC4E69EA1}"/>
+    <cellStyle name="Hyperlink 3" xfId="2" xr:uid="{6C374B17-1BAC-4D72-B4CA-E39C7FFD16E7}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="4" xr:uid="{BB27FC59-1F16-47DC-8DE2-AC8F75C96994}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{F41CDAF8-BF48-4D02-AEEF-ADBF2B5F51CA}"/>
+    <cellStyle name="Normal 4" xfId="1" xr:uid="{EFEB0EA8-2BC2-4B7B-A07E-13497616884B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1578,7 +1603,7 @@
     <col min="2" max="2" width="49.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" style="25" customWidth="1"/>
     <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" customWidth="1"/>
+    <col min="5" max="5" width="20.109375" customWidth="1"/>
     <col min="6" max="6" width="15.44140625" style="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.33203125" customWidth="1"/>
@@ -1622,2724 +1647,1284 @@
         <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="D1" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="E1" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="16" t="s">
+      <c r="H1" s="61" t="s">
+        <v>249</v>
+      </c>
+      <c r="I1" s="61" t="s">
+        <v>250</v>
+      </c>
+      <c r="J1" s="61" t="s">
+        <v>251</v>
+      </c>
+      <c r="K1" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="L1" s="63" t="s">
+        <v>254</v>
+      </c>
+      <c r="M1" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="N1" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="P1" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="Q1" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q1" s="16" t="s">
+      <c r="R1" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="V1" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="W1" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="X1" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y1" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z1" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA1" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB1" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC1" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD1" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE1" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF1" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG1" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="AH1" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI1" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ1" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK1" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AL1" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM1" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AN1" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="AO1" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="AP1" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="AQ1" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="AR1" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="AS1" s="16" t="s">
-        <v>54</v>
-      </c>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="16"/>
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16"/>
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16"/>
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16"/>
+      <c r="AQ1" s="16"/>
+      <c r="AR1" s="16"/>
+      <c r="AS1" s="16"/>
     </row>
     <row r="2" spans="1:45" ht="30" customHeight="1">
       <c r="A2" s="17" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>55</v>
+        <v>132</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>248</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M2" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O2" s="21">
-        <v>520</v>
-      </c>
-      <c r="P2" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="21">
-        <v>520</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S2" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T2" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U2" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V2" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W2" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X2" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y2" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="62" t="s">
+        <v>253</v>
+      </c>
+      <c r="I2" s="62" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="K2" s="67" t="s">
+        <v>256</v>
+      </c>
+      <c r="L2" s="68" t="s">
         <v>14</v>
       </c>
+      <c r="M2" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" s="66" t="s">
+        <v>44</v>
+      </c>
+      <c r="S2" s="65"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
       <c r="Z2" s="21"/>
       <c r="AA2" s="22"/>
       <c r="AB2" s="22"/>
       <c r="AC2" s="22"/>
       <c r="AD2" s="22"/>
       <c r="AE2" s="22"/>
-      <c r="AF2" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF2" s="22"/>
       <c r="AG2" s="22"/>
-      <c r="AH2" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI2" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ2" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK2" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL2" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM2" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN2" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="AO2" s="19" t="s">
-        <v>221</v>
-      </c>
+      <c r="AH2" s="22"/>
+      <c r="AI2" s="22"/>
+      <c r="AJ2" s="21"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="19"/>
       <c r="AP2" s="19"/>
-      <c r="AQ2" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR2" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS2" s="19" t="s">
-        <v>64</v>
-      </c>
+      <c r="AQ2" s="19"/>
+      <c r="AR2" s="19"/>
+      <c r="AS2" s="19"/>
     </row>
     <row r="3" spans="1:45" ht="30" customHeight="1">
       <c r="A3" s="17" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O3" s="21">
-        <v>520</v>
-      </c>
-      <c r="P3" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="21">
-        <v>520</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S3" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T3" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U3" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W3" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X3" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y3" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D3" s="60"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
       <c r="Z3" s="21"/>
       <c r="AA3" s="22"/>
       <c r="AB3" s="22"/>
       <c r="AC3" s="22"/>
       <c r="AD3" s="22"/>
       <c r="AE3" s="22"/>
-      <c r="AF3" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF3" s="22"/>
       <c r="AG3" s="22"/>
-      <c r="AH3" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI3" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ3" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK3" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL3" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM3" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN3" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="AO3" s="19" t="s">
-        <v>222</v>
-      </c>
+      <c r="AH3" s="22"/>
+      <c r="AI3" s="22"/>
+      <c r="AJ3" s="21"/>
+      <c r="AK3" s="32"/>
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="19"/>
+      <c r="AO3" s="19"/>
       <c r="AP3" s="19"/>
-      <c r="AQ3" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR3" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS3" s="19" t="s">
-        <v>64</v>
-      </c>
+      <c r="AQ3" s="19"/>
+      <c r="AR3" s="19"/>
+      <c r="AS3" s="19"/>
     </row>
     <row r="4" spans="1:45" ht="30" customHeight="1">
       <c r="A4" s="17" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M4" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O4" s="21">
-        <v>520</v>
-      </c>
-      <c r="P4" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="21">
-        <v>520</v>
-      </c>
-      <c r="R4" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S4" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T4" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U4" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V4" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W4" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X4" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y4" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D4" s="60"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
       <c r="Z4" s="21"/>
       <c r="AA4" s="22"/>
       <c r="AB4" s="22"/>
       <c r="AC4" s="22"/>
       <c r="AD4" s="22"/>
       <c r="AE4" s="22"/>
-      <c r="AF4" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF4" s="22"/>
       <c r="AG4" s="22"/>
-      <c r="AH4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ4" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK4" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL4" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM4" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN4" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="AO4" s="19" t="s">
-        <v>223</v>
-      </c>
+      <c r="AH4" s="22"/>
+      <c r="AI4" s="22"/>
+      <c r="AJ4" s="21"/>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="19"/>
+      <c r="AM4" s="19"/>
+      <c r="AN4" s="19"/>
+      <c r="AO4" s="19"/>
       <c r="AP4" s="19"/>
-      <c r="AQ4" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR4" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS4" s="19" t="s">
-        <v>64</v>
-      </c>
+      <c r="AQ4" s="19"/>
+      <c r="AR4" s="19"/>
+      <c r="AS4" s="19"/>
     </row>
     <row r="5" spans="1:45" s="36" customFormat="1" ht="30" customHeight="1">
       <c r="A5" s="30" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="J5" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="M5" s="33">
-        <v>7524</v>
-      </c>
-      <c r="N5" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="O5" s="33">
-        <v>520</v>
-      </c>
-      <c r="P5" s="33">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="33">
-        <v>520</v>
-      </c>
-      <c r="R5" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="S5" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="T5" s="33">
-        <v>7524</v>
-      </c>
-      <c r="U5" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="V5" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="W5" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="X5" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y5" s="33" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D5" s="60"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="33"/>
+      <c r="Y5" s="33"/>
       <c r="Z5" s="33"/>
       <c r="AA5" s="35"/>
       <c r="AB5" s="35"/>
       <c r="AC5" s="35"/>
       <c r="AD5" s="35"/>
       <c r="AE5" s="35"/>
-      <c r="AF5" s="35" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF5" s="35"/>
       <c r="AG5" s="35"/>
-      <c r="AH5" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI5" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ5" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK5" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL5" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM5" s="58" t="s">
-        <v>278</v>
-      </c>
-      <c r="AN5" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="AO5" s="32" t="s">
-        <v>224</v>
-      </c>
+      <c r="AH5" s="35"/>
+      <c r="AI5" s="35"/>
+      <c r="AJ5" s="33"/>
+      <c r="AK5" s="32"/>
+      <c r="AL5" s="32"/>
+      <c r="AM5" s="58"/>
+      <c r="AN5" s="32"/>
+      <c r="AO5" s="32"/>
       <c r="AP5" s="32"/>
-      <c r="AQ5" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR5" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS5" s="32" t="s">
-        <v>69</v>
-      </c>
+      <c r="AQ5" s="32"/>
+      <c r="AR5" s="32"/>
+      <c r="AS5" s="32"/>
     </row>
     <row r="6" spans="1:45" s="28" customFormat="1" ht="30" customHeight="1">
       <c r="A6" s="17" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M6" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" s="21">
-        <v>520</v>
-      </c>
-      <c r="P6" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="21">
-        <v>520</v>
-      </c>
-      <c r="R6" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S6" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T6" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U6" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V6" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W6" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X6" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y6" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D6" s="60"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="21"/>
       <c r="Z6" s="21"/>
       <c r="AA6" s="22"/>
       <c r="AB6" s="22"/>
       <c r="AC6" s="22"/>
       <c r="AD6" s="22"/>
       <c r="AE6" s="22"/>
-      <c r="AF6" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF6" s="22"/>
       <c r="AG6" s="22"/>
-      <c r="AH6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ6" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK6" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL6" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM6" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="AN6" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="AO6" s="19" t="s">
-        <v>225</v>
-      </c>
+      <c r="AH6" s="22"/>
+      <c r="AI6" s="22"/>
+      <c r="AJ6" s="21"/>
+      <c r="AK6" s="19"/>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="19"/>
       <c r="AP6" s="19"/>
-      <c r="AQ6" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR6" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS6" s="19" t="s">
-        <v>69</v>
-      </c>
+      <c r="AQ6" s="19"/>
+      <c r="AR6" s="19"/>
+      <c r="AS6" s="19"/>
     </row>
     <row r="7" spans="1:45" s="28" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="21">
-        <v>520</v>
-      </c>
-      <c r="P7" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="21">
-        <v>520</v>
-      </c>
-      <c r="R7" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S7" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T7" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U7" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V7" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W7" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X7" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y7" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D7" s="60"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21"/>
       <c r="Z7" s="21"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="22"/>
       <c r="AC7" s="22"/>
       <c r="AD7" s="22"/>
       <c r="AE7" s="22"/>
-      <c r="AF7" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF7" s="22"/>
       <c r="AG7" s="22"/>
-      <c r="AH7" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI7" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ7" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK7" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL7" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM7" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AN7" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="AO7" s="19" t="s">
-        <v>226</v>
-      </c>
+      <c r="AH7" s="22"/>
+      <c r="AI7" s="22"/>
+      <c r="AJ7" s="21"/>
+      <c r="AK7" s="19"/>
+      <c r="AL7" s="19"/>
+      <c r="AM7" s="19"/>
+      <c r="AN7" s="19"/>
+      <c r="AO7" s="19"/>
       <c r="AP7" s="19"/>
-      <c r="AQ7" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR7" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS7" s="19" t="s">
-        <v>69</v>
-      </c>
+      <c r="AQ7" s="19"/>
+      <c r="AR7" s="19"/>
+      <c r="AS7" s="19"/>
     </row>
     <row r="8" spans="1:45" ht="30" customHeight="1">
       <c r="A8" s="17" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" s="21">
-        <v>520</v>
-      </c>
-      <c r="P8" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="21">
-        <v>520</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S8" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T8" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U8" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V8" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W8" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X8" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y8" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D8" s="60"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
       <c r="Z8" s="21"/>
       <c r="AA8" s="22"/>
       <c r="AB8" s="22"/>
       <c r="AC8" s="22"/>
       <c r="AD8" s="22"/>
       <c r="AE8" s="22"/>
-      <c r="AF8" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF8" s="22"/>
       <c r="AG8" s="22"/>
-      <c r="AH8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ8" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK8" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL8" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM8" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH8" s="22"/>
+      <c r="AI8" s="22"/>
+      <c r="AJ8" s="21"/>
+      <c r="AK8" s="19"/>
+      <c r="AL8" s="19"/>
+      <c r="AM8" s="19"/>
       <c r="AN8" s="19"/>
       <c r="AO8" s="19"/>
       <c r="AP8" s="19"/>
-      <c r="AQ8" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR8" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS8" s="19" t="s">
-        <v>64</v>
-      </c>
+      <c r="AQ8" s="19"/>
+      <c r="AR8" s="19"/>
+      <c r="AS8" s="19"/>
     </row>
     <row r="9" spans="1:45" ht="30" customHeight="1">
       <c r="A9" s="17" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="21">
-        <v>520</v>
-      </c>
-      <c r="P9" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="21">
-        <v>520</v>
-      </c>
-      <c r="R9" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S9" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T9" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U9" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V9" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W9" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X9" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y9" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D9" s="60"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
       <c r="Z9" s="21"/>
       <c r="AA9" s="22"/>
       <c r="AB9" s="22"/>
       <c r="AC9" s="22"/>
       <c r="AD9" s="22"/>
       <c r="AE9" s="22"/>
-      <c r="AF9" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF9" s="22"/>
       <c r="AG9" s="22"/>
-      <c r="AH9" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI9" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ9" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK9" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL9" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM9" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH9" s="22"/>
+      <c r="AI9" s="22"/>
+      <c r="AJ9" s="21"/>
+      <c r="AK9" s="19"/>
+      <c r="AL9" s="19"/>
+      <c r="AM9" s="19"/>
       <c r="AN9" s="19"/>
       <c r="AO9" s="19"/>
       <c r="AP9" s="19"/>
-      <c r="AQ9" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR9" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS9" s="19" t="s">
-        <v>64</v>
-      </c>
+      <c r="AQ9" s="19"/>
+      <c r="AR9" s="19"/>
+      <c r="AS9" s="19"/>
     </row>
     <row r="10" spans="1:45" ht="30" customHeight="1">
       <c r="A10" s="17" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M10" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O10" s="21">
-        <v>520</v>
-      </c>
-      <c r="P10" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="21">
-        <v>520</v>
-      </c>
-      <c r="R10" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S10" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T10" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U10" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V10" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W10" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X10" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y10" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D10" s="60"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
       <c r="Z10" s="21"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="22"/>
       <c r="AC10" s="22"/>
       <c r="AD10" s="22"/>
       <c r="AE10" s="22"/>
-      <c r="AF10" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF10" s="22"/>
       <c r="AG10" s="22"/>
-      <c r="AH10" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI10" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ10" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK10" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL10" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM10" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH10" s="22"/>
+      <c r="AI10" s="22"/>
+      <c r="AJ10" s="21"/>
+      <c r="AK10" s="19"/>
+      <c r="AL10" s="19"/>
+      <c r="AM10" s="19"/>
       <c r="AN10" s="19"/>
       <c r="AO10" s="19"/>
       <c r="AP10" s="19"/>
-      <c r="AQ10" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR10" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS10" s="19" t="s">
-        <v>64</v>
-      </c>
+      <c r="AQ10" s="19"/>
+      <c r="AR10" s="19"/>
+      <c r="AS10" s="19"/>
     </row>
     <row r="11" spans="1:45" ht="30" customHeight="1">
       <c r="A11" s="17" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O11" s="21">
-        <v>520</v>
-      </c>
-      <c r="P11" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="21">
-        <v>520</v>
-      </c>
-      <c r="R11" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S11" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T11" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U11" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V11" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W11" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X11" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y11" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D11" s="60"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="21"/>
+      <c r="V11" s="21"/>
+      <c r="W11" s="21"/>
+      <c r="X11" s="21"/>
+      <c r="Y11" s="21"/>
       <c r="Z11" s="21"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="22"/>
       <c r="AC11" s="22"/>
       <c r="AD11" s="22"/>
       <c r="AE11" s="22"/>
-      <c r="AF11" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF11" s="22"/>
       <c r="AG11" s="22"/>
-      <c r="AH11" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI11" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ11" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK11" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="AL11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM11" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH11" s="22"/>
+      <c r="AI11" s="22"/>
+      <c r="AJ11" s="21"/>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="19"/>
       <c r="AN11" s="19"/>
       <c r="AO11" s="19"/>
       <c r="AP11" s="19"/>
-      <c r="AQ11" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR11" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS11" s="19" t="s">
-        <v>64</v>
-      </c>
+      <c r="AQ11" s="19"/>
+      <c r="AR11" s="19"/>
+      <c r="AS11" s="19"/>
     </row>
     <row r="12" spans="1:45" s="37" customFormat="1" ht="30" customHeight="1">
       <c r="A12" s="30" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="J12" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="K12" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="L12" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="M12" s="33">
-        <v>7524</v>
-      </c>
-      <c r="N12" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="O12" s="33">
-        <v>520</v>
-      </c>
-      <c r="P12" s="33">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="33">
-        <v>520</v>
-      </c>
-      <c r="R12" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="S12" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="T12" s="33">
-        <v>7524</v>
-      </c>
-      <c r="U12" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="V12" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="W12" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="X12" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y12" s="33" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D12" s="60"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="33"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
       <c r="Z12" s="33"/>
       <c r="AA12" s="35"/>
       <c r="AB12" s="35"/>
       <c r="AC12" s="35"/>
       <c r="AD12" s="35"/>
       <c r="AE12" s="35"/>
-      <c r="AF12" s="35" t="s">
-        <v>81</v>
-      </c>
+      <c r="AF12" s="35"/>
       <c r="AG12" s="35"/>
-      <c r="AH12" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI12" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ12" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK12" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL12" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM12" s="32" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH12" s="35"/>
+      <c r="AI12" s="35"/>
+      <c r="AJ12" s="33"/>
+      <c r="AK12" s="32"/>
+      <c r="AL12" s="32"/>
+      <c r="AM12" s="32"/>
       <c r="AN12" s="32"/>
       <c r="AO12" s="32"/>
       <c r="AP12" s="32"/>
-      <c r="AQ12" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR12" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS12" s="32" t="s">
-        <v>79</v>
-      </c>
+      <c r="AQ12" s="32"/>
+      <c r="AR12" s="32"/>
+      <c r="AS12" s="32"/>
     </row>
     <row r="13" spans="1:45" ht="30" customHeight="1">
       <c r="A13" s="17" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O13" s="21">
-        <v>520</v>
-      </c>
-      <c r="P13" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="21">
-        <v>520</v>
-      </c>
-      <c r="R13" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S13" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T13" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U13" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V13" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W13" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X13" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y13" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D13" s="60"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="21"/>
       <c r="Z13" s="21"/>
       <c r="AA13" s="22"/>
       <c r="AB13" s="22"/>
       <c r="AC13" s="22"/>
       <c r="AD13" s="22"/>
-      <c r="AF13" s="22" t="s">
-        <v>82</v>
-      </c>
+      <c r="AF13" s="22"/>
       <c r="AG13" s="22"/>
-      <c r="AH13" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI13" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ13" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK13" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="AL13" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM13" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH13" s="22"/>
+      <c r="AI13" s="22"/>
+      <c r="AJ13" s="21"/>
+      <c r="AK13" s="19"/>
+      <c r="AL13" s="19"/>
+      <c r="AM13" s="19"/>
       <c r="AN13" s="19"/>
       <c r="AO13" s="19"/>
       <c r="AP13" s="19"/>
-      <c r="AQ13" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR13" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS13" s="19" t="s">
-        <v>79</v>
-      </c>
+      <c r="AQ13" s="19"/>
+      <c r="AR13" s="19"/>
+      <c r="AS13" s="19"/>
     </row>
     <row r="14" spans="1:45" ht="30" customHeight="1">
       <c r="A14" s="17" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L14" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O14" s="21">
-        <v>520</v>
-      </c>
-      <c r="P14" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="21">
-        <v>520</v>
-      </c>
-      <c r="R14" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S14" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T14" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U14" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V14" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W14" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X14" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y14" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D14" s="60"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
       <c r="Z14" s="21"/>
       <c r="AA14" s="22"/>
       <c r="AB14" s="22"/>
       <c r="AC14" s="22"/>
       <c r="AD14" s="22"/>
       <c r="AE14" s="22"/>
-      <c r="AF14" s="15" t="s">
-        <v>262</v>
-      </c>
       <c r="AG14" s="22"/>
-      <c r="AH14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ14" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK14" s="19" t="s">
-        <v>277</v>
-      </c>
-      <c r="AL14" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM14" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH14" s="22"/>
+      <c r="AI14" s="22"/>
+      <c r="AJ14" s="21"/>
+      <c r="AK14" s="19"/>
+      <c r="AL14" s="19"/>
+      <c r="AM14" s="19"/>
       <c r="AN14" s="19"/>
       <c r="AO14" s="19"/>
       <c r="AP14" s="19"/>
-      <c r="AQ14" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR14" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS14" s="19" t="s">
-        <v>79</v>
-      </c>
+      <c r="AQ14" s="19"/>
+      <c r="AR14" s="19"/>
+      <c r="AS14" s="19"/>
     </row>
     <row r="15" spans="1:45" s="49" customFormat="1" ht="30" customHeight="1">
       <c r="A15" s="43" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="J15" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="K15" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="M15" s="46">
-        <v>7524</v>
-      </c>
-      <c r="N15" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="O15" s="46">
-        <v>520</v>
-      </c>
-      <c r="P15" s="46">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="46">
-        <v>520</v>
-      </c>
-      <c r="R15" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="S15" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="T15" s="46">
-        <v>7524</v>
-      </c>
-      <c r="U15" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="V15" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="W15" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="X15" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y15" s="46" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D15" s="60"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="46"/>
+      <c r="Y15" s="46"/>
       <c r="Z15" s="46"/>
       <c r="AA15" s="48"/>
       <c r="AB15" s="48"/>
       <c r="AC15" s="48"/>
       <c r="AD15" s="48"/>
       <c r="AE15" s="48"/>
-      <c r="AF15" s="22" t="s">
-        <v>263</v>
-      </c>
+      <c r="AF15" s="22"/>
       <c r="AG15" s="48"/>
-      <c r="AH15" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI15" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ15" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK15" s="45" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL15" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM15" s="45" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH15" s="48"/>
+      <c r="AI15" s="48"/>
+      <c r="AJ15" s="46"/>
+      <c r="AK15" s="45"/>
+      <c r="AL15" s="45"/>
+      <c r="AM15" s="45"/>
       <c r="AN15" s="45"/>
       <c r="AO15" s="45"/>
       <c r="AP15" s="45"/>
-      <c r="AQ15" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR15" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS15" s="45" t="s">
-        <v>79</v>
-      </c>
+      <c r="AQ15" s="45"/>
+      <c r="AR15" s="45"/>
+      <c r="AS15" s="45"/>
     </row>
     <row r="16" spans="1:45" ht="30" customHeight="1">
       <c r="A16" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>238</v>
-      </c>
       <c r="C16" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L16" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M16" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O16" s="21">
-        <v>520</v>
-      </c>
-      <c r="P16" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="21">
-        <v>520</v>
-      </c>
-      <c r="R16" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S16" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T16" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U16" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V16" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W16" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X16" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y16" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D16" s="60"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="21"/>
       <c r="Z16" s="21"/>
       <c r="AA16" s="22"/>
       <c r="AB16" s="22"/>
       <c r="AC16" s="22"/>
       <c r="AD16" s="22"/>
       <c r="AE16" s="22"/>
-      <c r="AF16" s="22" t="s">
-        <v>256</v>
-      </c>
+      <c r="AF16" s="22"/>
       <c r="AG16" s="22"/>
-      <c r="AH16" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI16" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ16" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK16" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL16" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM16" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH16" s="22"/>
+      <c r="AI16" s="22"/>
+      <c r="AJ16" s="21"/>
+      <c r="AK16" s="19"/>
+      <c r="AL16" s="19"/>
+      <c r="AM16" s="19"/>
       <c r="AN16" s="19"/>
       <c r="AO16" s="19"/>
       <c r="AP16" s="19"/>
-      <c r="AQ16" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR16" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS16" s="19" t="s">
-        <v>79</v>
-      </c>
+      <c r="AQ16" s="19"/>
+      <c r="AR16" s="19"/>
+      <c r="AS16" s="19"/>
     </row>
     <row r="17" spans="1:45" s="37" customFormat="1" ht="30" customHeight="1">
       <c r="A17" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="B17" s="31" t="s">
-        <v>239</v>
-      </c>
       <c r="C17" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="G17" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H17" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="K17" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="L17" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="M17" s="32">
-        <v>100</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D17" s="60"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="32"/>
       <c r="N17" s="38"/>
       <c r="O17" s="32"/>
-      <c r="P17" s="33">
-        <v>1</v>
-      </c>
+      <c r="P17" s="33"/>
       <c r="Q17" s="39"/>
-      <c r="R17" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="S17" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="T17" s="33">
-        <v>7524</v>
-      </c>
-      <c r="U17" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="V17" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="W17" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="X17" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y17" s="33" t="s">
-        <v>14</v>
-      </c>
+      <c r="R17" s="34"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
+      <c r="Y17" s="33"/>
       <c r="Z17" s="32"/>
       <c r="AA17" s="40"/>
       <c r="AB17" s="40"/>
       <c r="AC17" s="40"/>
       <c r="AD17" s="40"/>
       <c r="AE17" s="40"/>
-      <c r="AF17" s="42">
-        <v>1096</v>
-      </c>
+      <c r="AF17" s="42"/>
       <c r="AG17" s="35"/>
-      <c r="AH17" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI17" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ17" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK17" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL17" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM17" s="32" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH17" s="35"/>
+      <c r="AI17" s="35"/>
+      <c r="AJ17" s="33"/>
+      <c r="AK17" s="32"/>
+      <c r="AL17" s="19"/>
+      <c r="AM17" s="32"/>
       <c r="AN17" s="32"/>
       <c r="AO17" s="32"/>
       <c r="AP17" s="32"/>
-      <c r="AQ17" s="32" t="s">
-        <v>79</v>
-      </c>
+      <c r="AQ17" s="32"/>
       <c r="AR17" s="41"/>
-      <c r="AS17" s="32" t="s">
-        <v>79</v>
-      </c>
+      <c r="AS17" s="32"/>
     </row>
     <row r="18" spans="1:45" ht="30" customHeight="1">
       <c r="A18" s="17" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="M18" s="19">
-        <v>100</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D18" s="60"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="19"/>
       <c r="N18" s="13"/>
       <c r="O18" s="19"/>
-      <c r="P18" s="21">
-        <v>1</v>
-      </c>
+      <c r="P18" s="21"/>
       <c r="Q18" s="23"/>
-      <c r="R18" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S18" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T18" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U18" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V18" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W18" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X18" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y18" s="21" t="s">
-        <v>14</v>
-      </c>
+      <c r="R18" s="10"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="21"/>
+      <c r="V18" s="21"/>
+      <c r="W18" s="21"/>
+      <c r="X18" s="21"/>
+      <c r="Y18" s="21"/>
       <c r="Z18" s="19"/>
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20"/>
       <c r="AD18" s="20"/>
       <c r="AE18" s="20"/>
-      <c r="AF18" s="15" t="s">
-        <v>260</v>
-      </c>
       <c r="AG18" s="22"/>
-      <c r="AH18" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI18" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ18" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK18" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL18" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="AM18" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH18" s="22"/>
+      <c r="AI18" s="22"/>
+      <c r="AJ18" s="21"/>
+      <c r="AK18" s="19"/>
+      <c r="AL18" s="19"/>
+      <c r="AM18" s="19"/>
       <c r="AN18" s="19"/>
       <c r="AO18" s="19"/>
       <c r="AP18" s="19"/>
-      <c r="AQ18" s="32" t="s">
-        <v>79</v>
-      </c>
+      <c r="AQ18" s="32"/>
       <c r="AR18" s="41"/>
-      <c r="AS18" s="32" t="s">
-        <v>79</v>
-      </c>
+      <c r="AS18" s="32"/>
     </row>
     <row r="19" spans="1:45" ht="30" customHeight="1">
       <c r="A19" s="17" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>58</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D19" s="60"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
       <c r="M19" s="21"/>
-      <c r="N19" s="17" t="s">
-        <v>58</v>
-      </c>
+      <c r="N19" s="17"/>
       <c r="O19" s="21"/>
-      <c r="P19" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="21">
-        <v>520</v>
-      </c>
-      <c r="R19" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S19" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T19" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U19" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V19" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W19" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X19" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y19" s="21" t="e">
-        <f t="shared" ref="Y19:Y20" si="0">#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+      <c r="Y19" s="21"/>
       <c r="Z19" s="19"/>
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20"/>
       <c r="AD19" s="20"/>
       <c r="AE19" s="20"/>
-      <c r="AF19" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF19" s="22"/>
       <c r="AG19" s="22"/>
-      <c r="AH19" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI19" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ19" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK19" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL19" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM19" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH19" s="22"/>
+      <c r="AI19" s="22"/>
+      <c r="AJ19" s="21"/>
+      <c r="AK19" s="19"/>
+      <c r="AL19" s="19"/>
+      <c r="AM19" s="19"/>
       <c r="AN19" s="19"/>
       <c r="AO19" s="19"/>
       <c r="AP19" s="19"/>
-      <c r="AQ19" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR19" s="50" t="s">
-        <v>257</v>
-      </c>
-      <c r="AS19" s="19" t="s">
-        <v>69</v>
-      </c>
+      <c r="AQ19" s="19"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="19"/>
     </row>
     <row r="20" spans="1:45" ht="30" customHeight="1">
       <c r="A20" s="17" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M20" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O20" s="21">
-        <v>520</v>
-      </c>
-      <c r="P20" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="21">
-        <v>520</v>
-      </c>
-      <c r="R20" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S20" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T20" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U20" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V20" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W20" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X20" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y20" s="21" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D20" s="60"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="21"/>
+      <c r="X20" s="21"/>
+      <c r="Y20" s="21"/>
       <c r="Z20" s="19"/>
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20"/>
       <c r="AD20" s="20"/>
       <c r="AE20" s="20"/>
-      <c r="AF20" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF20" s="22"/>
       <c r="AG20" s="22"/>
-      <c r="AH20" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI20" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ20" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK20" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL20" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM20" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH20" s="22"/>
+      <c r="AI20" s="22"/>
+      <c r="AJ20" s="21"/>
+      <c r="AK20" s="19"/>
+      <c r="AL20" s="19"/>
+      <c r="AM20" s="19"/>
       <c r="AN20" s="19"/>
       <c r="AO20" s="19"/>
       <c r="AP20" s="19"/>
-      <c r="AQ20" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR20" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS20" s="19" t="s">
-        <v>69</v>
-      </c>
+      <c r="AQ20" s="19"/>
+      <c r="AR20" s="19"/>
+      <c r="AS20" s="19"/>
     </row>
     <row r="21" spans="1:45" ht="30" customHeight="1">
       <c r="A21" s="17" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J21" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M21" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O21" s="21">
-        <v>520</v>
-      </c>
-      <c r="P21" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="21">
-        <v>520</v>
-      </c>
-      <c r="R21" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S21" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T21" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U21" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V21" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W21" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X21" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y21" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D21" s="60"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="21"/>
+      <c r="V21" s="21"/>
+      <c r="W21" s="21"/>
+      <c r="X21" s="21"/>
+      <c r="Y21" s="21"/>
       <c r="Z21" s="21"/>
       <c r="AA21" s="22"/>
       <c r="AB21" s="22"/>
       <c r="AC21" s="22"/>
       <c r="AD21" s="22"/>
       <c r="AE21" s="22"/>
-      <c r="AF21" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF21" s="22"/>
       <c r="AG21" s="22"/>
-      <c r="AH21" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI21" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ21" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK21" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL21" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM21" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH21" s="22"/>
+      <c r="AI21" s="22"/>
+      <c r="AJ21" s="21"/>
+      <c r="AK21" s="19"/>
+      <c r="AL21" s="19"/>
+      <c r="AM21" s="19"/>
       <c r="AN21" s="19"/>
       <c r="AO21" s="19"/>
       <c r="AP21" s="19"/>
-      <c r="AQ21" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR21" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS21" s="19" t="s">
-        <v>69</v>
-      </c>
+      <c r="AQ21" s="19"/>
+      <c r="AR21" s="19"/>
+      <c r="AS21" s="19"/>
     </row>
     <row r="22" spans="1:45" s="15" customFormat="1" ht="30" customHeight="1">
       <c r="A22" s="17" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L22" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M22" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O22" s="21">
-        <v>520</v>
-      </c>
-      <c r="P22" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="21">
-        <v>520</v>
-      </c>
-      <c r="R22" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S22" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T22" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U22" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V22" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W22" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X22" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y22" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D22" s="60"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="21"/>
+      <c r="V22" s="21"/>
+      <c r="W22" s="21"/>
+      <c r="X22" s="21"/>
+      <c r="Y22" s="21"/>
       <c r="Z22" s="21"/>
       <c r="AA22" s="22"/>
       <c r="AB22" s="22"/>
       <c r="AC22" s="22"/>
       <c r="AD22" s="22"/>
       <c r="AE22" s="22"/>
-      <c r="AF22" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF22" s="22"/>
       <c r="AG22" s="22"/>
-      <c r="AH22" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI22" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ22" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK22" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL22" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM22" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH22" s="22"/>
+      <c r="AI22" s="22"/>
+      <c r="AJ22" s="21"/>
+      <c r="AK22" s="19"/>
+      <c r="AL22" s="19"/>
+      <c r="AM22" s="19"/>
       <c r="AN22" s="19"/>
       <c r="AO22" s="19"/>
       <c r="AP22" s="19"/>
-      <c r="AQ22" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR22" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS22" s="19" t="s">
-        <v>64</v>
-      </c>
+      <c r="AQ22" s="19"/>
+      <c r="AR22" s="19"/>
+      <c r="AS22" s="19"/>
     </row>
     <row r="23" spans="1:45" s="15" customFormat="1" ht="30" customHeight="1">
       <c r="A23" s="17" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="K23" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L23" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="M23" s="21">
-        <v>7524</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="O23" s="21">
-        <v>520</v>
-      </c>
-      <c r="P23" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="21">
-        <v>520</v>
-      </c>
-      <c r="R23" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S23" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="T23" s="21">
-        <v>7524</v>
-      </c>
-      <c r="U23" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="V23" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="W23" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="X23" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y23" s="21" t="s">
-        <v>14</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D23" s="60"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="21"/>
+      <c r="V23" s="21"/>
+      <c r="W23" s="21"/>
+      <c r="X23" s="21"/>
+      <c r="Y23" s="21"/>
       <c r="Z23" s="21"/>
       <c r="AA23" s="22"/>
       <c r="AB23" s="22"/>
       <c r="AC23" s="22"/>
       <c r="AD23" s="22"/>
       <c r="AE23" s="22"/>
-      <c r="AF23" s="22" t="s">
-        <v>61</v>
-      </c>
+      <c r="AF23" s="22"/>
       <c r="AG23" s="22"/>
-      <c r="AH23" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI23" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ23" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK23" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL23" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM23" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="AH23" s="22"/>
+      <c r="AI23" s="22"/>
+      <c r="AJ23" s="21"/>
+      <c r="AK23" s="19"/>
+      <c r="AL23" s="19"/>
+      <c r="AM23" s="19"/>
       <c r="AN23" s="19"/>
       <c r="AO23" s="19"/>
       <c r="AP23" s="19"/>
-      <c r="AQ23" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR23" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS23" s="19" t="s">
-        <v>64</v>
-      </c>
+      <c r="AQ23" s="19"/>
+      <c r="AR23" s="19"/>
+      <c r="AS23" s="19"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="13">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AL2:AL17 AL19:AL23" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Positive,Negative"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G12:G19 D23 D2:D7 G2:G8 D9 D12:D19 D21" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G12:G19 G2:G8" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"ADD,CHOOSE,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G20:G21 G10:G11 D10:D11 D20" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G20:G21 G10:G11" xr:uid="{00000000-0002-0000-0100-000005000000}">
       <formula1>"ADD,CHOOSE,NO,CHANGE"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AL18" xr:uid="{00000000-0002-0000-0100-000006000000}">
@@ -4360,7 +2945,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F23 I2:I23" xr:uid="{00C061CC-BD68-4E32-A500-741692BE7860}">
       <formula1>"RANDOM"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C23 D22 G22:G23" xr:uid="{1FA657E6-88DD-41F4-8CD9-9A690EB78001}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G22:G23 C2:C23" xr:uid="{1FA657E6-88DD-41F4-8CD9-9A690EB78001}">
       <formula1>"MANUAL, BULKUPLOAD"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H23 E2:E23" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -4434,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>26</v>
@@ -4443,141 +3028,141 @@
         <v>27</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="U1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="V1" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="X1" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z1" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA1" s="8" t="s">
-        <v>103</v>
-      </c>
       <c r="AB1" s="29" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AC1" s="29" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="AD1" s="29" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AE1" s="29" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="AF1" s="16" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AG1" s="16" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="AH1" s="16" t="s">
         <v>8</v>
       </c>
       <c r="AI1" s="16" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="AJ1" s="16" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="AK1" s="16" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="AL1" s="16" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="AM1" s="16" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AN1" s="16" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="AO1" s="16" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="30" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J2" s="10">
         <v>15000</v>
@@ -4586,7 +3171,7 @@
         <v>45056</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M2" s="10">
         <v>1250</v>
@@ -4595,28 +3180,28 @@
         <v>65415</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P2" s="10">
         <v>850</v>
       </c>
       <c r="Q2" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R2" s="10">
         <v>48514</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T2" s="10">
         <v>987456321</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W2" s="10">
         <v>7524</v>
@@ -4631,10 +3216,10 @@
         <v>520</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB2" s="22" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC2" s="22"/>
       <c r="AD2" s="22" t="s">
@@ -4644,61 +3229,61 @@
         <v>14</v>
       </c>
       <c r="AF2" s="21" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG2" s="19" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH2" s="19" t="s">
         <v>15</v>
       </c>
       <c r="AI2" s="19" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ2" s="19" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="AK2" s="19" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="AL2" s="19"/>
       <c r="AM2" s="19" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AN2" s="19" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO2" s="19" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="30" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J3" s="10">
         <v>15000</v>
@@ -4707,7 +3292,7 @@
         <v>45056</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M3" s="10">
         <v>1250</v>
@@ -4716,28 +3301,28 @@
         <v>65415</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P3" s="10">
         <v>850</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R3" s="10">
         <v>48514</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T3" s="10">
         <v>987456321</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W3" s="10">
         <v>7524</v>
@@ -4752,10 +3337,10 @@
         <v>520</v>
       </c>
       <c r="AA3" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB3" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC3" s="51"/>
       <c r="AD3" s="51" t="s">
@@ -4765,61 +3350,61 @@
         <v>14</v>
       </c>
       <c r="AF3" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG3" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH3" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI3" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ3" s="53" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="AK3" s="53" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="AL3" s="53"/>
       <c r="AM3" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AN3" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO3" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:41" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J4" s="10">
         <v>15000</v>
@@ -4828,7 +3413,7 @@
         <v>45056</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M4" s="10">
         <v>1250</v>
@@ -4837,28 +3422,28 @@
         <v>65415</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P4" s="10">
         <v>850</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R4" s="10">
         <v>48514</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T4" s="10">
         <v>987456321</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W4" s="10">
         <v>7524</v>
@@ -4873,10 +3458,10 @@
         <v>520</v>
       </c>
       <c r="AA4" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB4" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC4" s="51"/>
       <c r="AD4" s="51" t="s">
@@ -4886,61 +3471,61 @@
         <v>14</v>
       </c>
       <c r="AF4" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG4" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH4" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI4" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ4" s="53" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="AK4" s="53" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="AL4" s="53"/>
       <c r="AM4" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AN4" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO4" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:41" ht="30" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J5" s="10">
         <v>15000</v>
@@ -4949,7 +3534,7 @@
         <v>45056</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M5" s="10">
         <v>1250</v>
@@ -4958,28 +3543,28 @@
         <v>65415</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P5" s="10">
         <v>850</v>
       </c>
       <c r="Q5" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R5" s="10">
         <v>48514</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T5" s="10">
         <v>987456321</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V5" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W5" s="10">
         <v>7524</v>
@@ -4994,10 +3579,10 @@
         <v>520</v>
       </c>
       <c r="AA5" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB5" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC5" s="51"/>
       <c r="AD5" s="51" t="s">
@@ -5007,61 +3592,61 @@
         <v>14</v>
       </c>
       <c r="AF5" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG5" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH5" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI5" s="53" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="AJ5" s="53" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="AK5" s="53" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="AL5" s="53"/>
       <c r="AM5" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AN5" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO5" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:41" ht="30" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J6" s="10">
         <v>15000</v>
@@ -5070,7 +3655,7 @@
         <v>45056</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M6" s="10">
         <v>1250</v>
@@ -5079,28 +3664,28 @@
         <v>65415</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P6" s="10">
         <v>850</v>
       </c>
       <c r="Q6" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R6" s="10">
         <v>48514</v>
       </c>
       <c r="S6" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T6" s="10">
         <v>987456321</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W6" s="10">
         <v>7524</v>
@@ -5115,10 +3700,10 @@
         <v>520</v>
       </c>
       <c r="AA6" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB6" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC6" s="51"/>
       <c r="AD6" s="51" t="s">
@@ -5128,61 +3713,61 @@
         <v>14</v>
       </c>
       <c r="AF6" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG6" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH6" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI6" s="53" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="AJ6" s="53" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="AK6" s="53" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="AL6" s="53"/>
       <c r="AM6" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AN6" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO6" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:41" ht="30" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J7" s="10">
         <v>15000</v>
@@ -5191,7 +3776,7 @@
         <v>45056</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M7" s="10">
         <v>1250</v>
@@ -5200,28 +3785,28 @@
         <v>65415</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P7" s="10">
         <v>850</v>
       </c>
       <c r="Q7" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R7" s="10">
         <v>48514</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T7" s="10">
         <v>987456321</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W7" s="10">
         <v>7524</v>
@@ -5236,10 +3821,10 @@
         <v>520</v>
       </c>
       <c r="AA7" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB7" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC7" s="51"/>
       <c r="AD7" s="51" t="s">
@@ -5249,61 +3834,61 @@
         <v>14</v>
       </c>
       <c r="AF7" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG7" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH7" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI7" s="53" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="AJ7" s="53" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="AK7" s="53" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="AL7" s="53"/>
       <c r="AM7" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AN7" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO7" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:41" ht="30" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>158</v>
-      </c>
       <c r="D8" s="17" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J8" s="10">
         <v>15000</v>
@@ -5312,7 +3897,7 @@
         <v>45056</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M8" s="10">
         <v>1250</v>
@@ -5321,28 +3906,28 @@
         <v>65415</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P8" s="10">
         <v>850</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R8" s="10">
         <v>48514</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T8" s="10">
         <v>987456321</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W8" s="10">
         <v>7524</v>
@@ -5357,10 +3942,10 @@
         <v>520</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB8" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC8" s="51"/>
       <c r="AD8" s="51" t="s">
@@ -5370,57 +3955,57 @@
         <v>14</v>
       </c>
       <c r="AF8" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG8" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH8" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI8" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ8" s="53"/>
       <c r="AK8" s="53"/>
       <c r="AL8" s="53"/>
       <c r="AM8" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AN8" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO8" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:41" ht="30" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>158</v>
-      </c>
       <c r="D9" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J9" s="10">
         <v>15000</v>
@@ -5429,7 +4014,7 @@
         <v>45056</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M9" s="10">
         <v>1250</v>
@@ -5438,28 +4023,28 @@
         <v>65415</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P9" s="10">
         <v>850</v>
       </c>
       <c r="Q9" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R9" s="10">
         <v>48514</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T9" s="10">
         <v>987456321</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W9" s="10">
         <v>7524</v>
@@ -5474,10 +4059,10 @@
         <v>520</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB9" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC9" s="51"/>
       <c r="AD9" s="51" t="s">
@@ -5487,57 +4072,57 @@
         <v>14</v>
       </c>
       <c r="AF9" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG9" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH9" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI9" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ9" s="53"/>
       <c r="AK9" s="53"/>
       <c r="AL9" s="53"/>
       <c r="AM9" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AN9" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO9" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:41" ht="30" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J10" s="10">
         <v>15000</v>
@@ -5546,7 +4131,7 @@
         <v>45056</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M10" s="10">
         <v>1250</v>
@@ -5555,28 +4140,28 @@
         <v>65415</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P10" s="10">
         <v>850</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R10" s="10">
         <v>48514</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T10" s="10">
         <v>987456321</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W10" s="10">
         <v>7524</v>
@@ -5591,10 +4176,10 @@
         <v>520</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB10" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC10" s="51"/>
       <c r="AD10" s="51" t="s">
@@ -5604,57 +4189,57 @@
         <v>14</v>
       </c>
       <c r="AF10" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG10" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH10" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI10" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ10" s="53"/>
       <c r="AK10" s="53"/>
       <c r="AL10" s="53"/>
       <c r="AM10" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AN10" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO10" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:41" ht="30" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J11" s="10">
         <v>15000</v>
@@ -5663,7 +4248,7 @@
         <v>45056</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M11" s="10">
         <v>1250</v>
@@ -5672,28 +4257,28 @@
         <v>65415</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P11" s="10">
         <v>850</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R11" s="10">
         <v>48514</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T11" s="10">
         <v>987456321</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V11" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W11" s="10">
         <v>7524</v>
@@ -5708,10 +4293,10 @@
         <v>520</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB11" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC11" s="51"/>
       <c r="AD11" s="51" t="s">
@@ -5721,57 +4306,57 @@
         <v>14</v>
       </c>
       <c r="AF11" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG11" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH11" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI11" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ11" s="53"/>
       <c r="AK11" s="53"/>
       <c r="AL11" s="53"/>
       <c r="AM11" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AN11" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO11" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:41" ht="30" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J12" s="10">
         <v>15000</v>
@@ -5780,7 +4365,7 @@
         <v>45056</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M12" s="10">
         <v>1250</v>
@@ -5789,28 +4374,28 @@
         <v>65415</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P12" s="10">
         <v>850</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R12" s="10">
         <v>48514</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T12" s="10">
         <v>987456321</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W12" s="10">
         <v>7524</v>
@@ -5825,10 +4410,10 @@
         <v>520</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB12" s="51" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="AC12" s="51"/>
       <c r="AD12" s="51" t="s">
@@ -5838,57 +4423,57 @@
         <v>14</v>
       </c>
       <c r="AF12" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG12" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH12" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI12" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ12" s="53"/>
       <c r="AK12" s="53"/>
       <c r="AL12" s="53"/>
       <c r="AM12" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="AN12" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO12" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:41" ht="30" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J13" s="10">
         <v>15000</v>
@@ -5897,7 +4482,7 @@
         <v>45056</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M13" s="10">
         <v>1250</v>
@@ -5906,28 +4491,28 @@
         <v>65415</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P13" s="10">
         <v>850</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R13" s="10">
         <v>48514</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T13" s="10">
         <v>987456321</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W13" s="10">
         <v>7524</v>
@@ -5942,10 +4527,10 @@
         <v>520</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB13" s="51" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="AC13" s="51"/>
       <c r="AD13" s="51" t="s">
@@ -5955,57 +4540,57 @@
         <v>14</v>
       </c>
       <c r="AF13" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG13" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH13" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI13" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ13" s="53"/>
       <c r="AK13" s="53"/>
       <c r="AL13" s="53"/>
       <c r="AM13" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="AN13" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO13" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:41" ht="30" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J14" s="10">
         <v>15000</v>
@@ -6014,7 +4599,7 @@
         <v>45056</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M14" s="10">
         <v>1250</v>
@@ -6023,28 +4608,28 @@
         <v>65415</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P14" s="10">
         <v>850</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R14" s="10">
         <v>48514</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T14" s="10">
         <v>987456321</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W14" s="10">
         <v>7524</v>
@@ -6059,10 +4644,10 @@
         <v>520</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB14" s="54" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="AC14" s="51"/>
       <c r="AD14" s="51" t="s">
@@ -6072,57 +4657,57 @@
         <v>14</v>
       </c>
       <c r="AF14" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG14" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH14" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI14" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ14" s="53"/>
       <c r="AK14" s="53"/>
       <c r="AL14" s="53"/>
       <c r="AM14" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="AN14" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO14" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:41" ht="30" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I15" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J15" s="10">
         <v>15000</v>
@@ -6131,7 +4716,7 @@
         <v>45056</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M15" s="10">
         <v>1250</v>
@@ -6140,28 +4725,28 @@
         <v>65415</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P15" s="10">
         <v>850</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R15" s="10">
         <v>48514</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T15" s="10">
         <v>987456321</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W15" s="10">
         <v>7524</v>
@@ -6176,10 +4761,10 @@
         <v>520</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB15" s="51" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="AC15" s="51"/>
       <c r="AD15" s="51" t="s">
@@ -6189,57 +4774,57 @@
         <v>14</v>
       </c>
       <c r="AF15" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG15" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH15" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI15" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ15" s="53"/>
       <c r="AK15" s="53"/>
       <c r="AL15" s="53"/>
       <c r="AM15" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="AN15" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO15" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:41" ht="30" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J16" s="10">
         <v>15000</v>
@@ -6248,7 +4833,7 @@
         <v>45056</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M16" s="10">
         <v>1250</v>
@@ -6257,28 +4842,28 @@
         <v>65415</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P16" s="10">
         <v>850</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R16" s="10">
         <v>48514</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T16" s="10">
         <v>987456321</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W16" s="10">
         <v>7524</v>
@@ -6293,10 +4878,10 @@
         <v>520</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB16" s="51" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="AC16" s="51"/>
       <c r="AD16" s="51" t="s">
@@ -6306,57 +4891,57 @@
         <v>14</v>
       </c>
       <c r="AF16" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG16" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH16" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI16" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ16" s="53"/>
       <c r="AK16" s="53"/>
       <c r="AL16" s="53"/>
       <c r="AM16" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="AN16" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO16" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:41" ht="30" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J17" s="10">
         <v>15000</v>
@@ -6365,7 +4950,7 @@
         <v>45056</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M17" s="10">
         <v>1250</v>
@@ -6374,28 +4959,28 @@
         <v>65415</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P17" s="10">
         <v>850</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R17" s="10">
         <v>48514</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T17" s="10">
         <v>987456321</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W17" s="10">
         <v>7524</v>
@@ -6410,7 +4995,7 @@
         <v>520</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB17" s="55">
         <v>1096</v>
@@ -6423,55 +5008,55 @@
         <v>14</v>
       </c>
       <c r="AF17" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG17" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH17" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI17" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ17" s="53"/>
       <c r="AK17" s="53"/>
       <c r="AL17" s="53"/>
       <c r="AM17" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="AN17" s="56"/>
       <c r="AO17" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:41" ht="30" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J18" s="10">
         <v>15000</v>
@@ -6480,7 +5065,7 @@
         <v>45056</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M18" s="10">
         <v>1250</v>
@@ -6489,28 +5074,28 @@
         <v>65415</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P18" s="10">
         <v>850</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R18" s="10">
         <v>48514</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T18" s="10">
         <v>987456321</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W18" s="10">
         <v>7524</v>
@@ -6525,10 +5110,10 @@
         <v>520</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB18" s="54" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="AC18" s="51"/>
       <c r="AD18" s="51" t="s">
@@ -6538,61 +5123,61 @@
         <v>14</v>
       </c>
       <c r="AF18" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG18" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH18" s="53" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="AI18" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ18" s="53"/>
       <c r="AK18" s="53"/>
       <c r="AL18" s="53"/>
       <c r="AM18" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="AN18" s="56"/>
       <c r="AO18" s="53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:41" ht="30" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="K19" s="12">
         <v>45056</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M19" s="10">
         <v>1250</v>
@@ -6601,28 +5186,28 @@
         <v>65415</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P19" s="10">
         <v>850</v>
       </c>
       <c r="Q19" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R19" s="10">
         <v>48514</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T19" s="10">
         <v>987456321</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W19" s="10">
         <v>7524</v>
@@ -6637,10 +5222,10 @@
         <v>520</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB19" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC19" s="51"/>
       <c r="AD19" s="51" t="s">
@@ -6650,57 +5235,57 @@
         <v>14</v>
       </c>
       <c r="AF19" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG19" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH19" s="53" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="AI19" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ19" s="53"/>
       <c r="AK19" s="53"/>
       <c r="AL19" s="53"/>
       <c r="AM19" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AN19" s="57" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="AO19" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="30" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>14</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G20" s="17" t="s">
         <v>14</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J20" s="10">
         <v>15000</v>
@@ -6709,7 +5294,7 @@
         <v>45056</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M20" s="10">
         <v>1250</v>
@@ -6718,28 +5303,28 @@
         <v>65415</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P20" s="10">
         <v>850</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R20" s="10">
         <v>48514</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T20" s="10">
         <v>987456321</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W20" s="10">
         <v>7524</v>
@@ -6754,10 +5339,10 @@
         <v>520</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB20" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC20" s="51"/>
       <c r="AD20" s="51" t="s">
@@ -6767,57 +5352,57 @@
         <v>14</v>
       </c>
       <c r="AF20" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG20" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH20" s="53" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="AI20" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ20" s="53"/>
       <c r="AK20" s="53"/>
       <c r="AL20" s="53"/>
       <c r="AM20" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AN20" s="53" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="AO20" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="30" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G21" s="17" t="s">
         <v>14</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J21" s="10">
         <v>15000</v>
@@ -6826,7 +5411,7 @@
         <v>45056</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M21" s="10">
         <v>1250</v>
@@ -6835,28 +5420,28 @@
         <v>65415</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P21" s="10">
         <v>850</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R21" s="10">
         <v>48514</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T21" s="10">
         <v>987456321</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W21" s="10">
         <v>7524</v>
@@ -6871,10 +5456,10 @@
         <v>520</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB21" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC21" s="51"/>
       <c r="AD21" s="51" t="s">
@@ -6884,57 +5469,57 @@
         <v>14</v>
       </c>
       <c r="AF21" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG21" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH21" s="53" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="AI21" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ21" s="53"/>
       <c r="AK21" s="53"/>
       <c r="AL21" s="53"/>
       <c r="AM21" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AN21" s="53" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AO21" s="53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:41" ht="30" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="J22" s="10">
         <v>15000</v>
@@ -6943,7 +5528,7 @@
         <v>45056</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="M22" s="10">
         <v>1250</v>
@@ -6952,28 +5537,28 @@
         <v>65415</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P22" s="10">
         <v>850</v>
       </c>
       <c r="Q22" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="R22" s="10">
         <v>48514</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="T22" s="10">
         <v>987456321</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="W22" s="10">
         <v>7524</v>
@@ -6988,10 +5573,10 @@
         <v>520</v>
       </c>
       <c r="AA22" s="10" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="AB22" s="51" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="AC22" s="51"/>
       <c r="AD22" s="51" t="s">
@@ -7001,32 +5586,32 @@
         <v>14</v>
       </c>
       <c r="AF22" s="52" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AG22" s="53" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="AH22" s="53" t="s">
         <v>15</v>
       </c>
       <c r="AI22" s="53" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AJ22" s="53"/>
       <c r="AK22" s="53"/>
       <c r="AL22" s="53"/>
       <c r="AM22" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="AN22" s="53" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AO22" s="53" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AH2:AH17 AH19:AH22" xr:uid="{BFC3E247-DB73-42D6-BC2F-0FA0E299AD60}">
       <formula1>"Positive,Negative"</formula1>
@@ -7081,418 +5666,418 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1">
       <c r="A1" s="26" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1">
       <c r="A3" s="27" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1">
       <c r="A4" s="27" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1">
       <c r="A5" s="27" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1">
       <c r="A6" s="27" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1">
       <c r="A7" s="27" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1">
       <c r="A8" s="27" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1">
       <c r="A9" s="27" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1">
       <c r="A13" s="27" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1">
       <c r="A14" s="27" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="27" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="27" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="27" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" customHeight="1">
       <c r="A21" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="24" t="s">
         <v>169</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" customHeight="1">
       <c r="A22" s="27" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1">
       <c r="A23" s="27" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="30" customHeight="1">
       <c r="A24" s="27" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" customHeight="1">
       <c r="A25" s="27" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" customHeight="1">
       <c r="A26" s="27" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" customHeight="1">
       <c r="A27" s="27" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" customHeight="1">
       <c r="A28" s="27" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" customHeight="1">
       <c r="A29" s="27" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="30" customHeight="1">
       <c r="A30" s="27" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="30" customHeight="1">
       <c r="A31" s="27" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="30" customHeight="1">
       <c r="A32" s="27" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="30" customHeight="1">
       <c r="A33" s="27" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30" customHeight="1">
       <c r="A34" s="27" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="30" customHeight="1">
       <c r="A35" s="27" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="30" customHeight="1">
       <c r="A36" s="27" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="30" customHeight="1">
       <c r="A37" s="27" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="30" customHeight="1">
       <c r="A38" s="27" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="30" customHeight="1">
       <c r="A39" s="27" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="30" customHeight="1">
       <c r="A40" s="27" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="30" customHeight="1">
       <c r="A41" s="27" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="30" customHeight="1">
       <c r="A42" s="27" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="30" customHeight="1">
       <c r="A43" s="27" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="30" customHeight="1">
       <c r="A44" s="27" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="30" customHeight="1">
       <c r="A45" s="27" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="30" customHeight="1">
       <c r="A46" s="27" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="30" customHeight="1">
       <c r="A47" s="27" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="30" customHeight="1">
       <c r="A48" s="27" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" customHeight="1">
       <c r="A49" s="27" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="30" customHeight="1">
       <c r="A50" s="27" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="30" customHeight="1">
       <c r="A51" s="27" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="30" customHeight="1">
       <c r="A52" s="27" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
